--- a/www/ig/fhir/core/StructureDefinition-fr-core-appointment.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-appointment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="407">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Appointment</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Appointment|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -430,7 +430,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -443,14 +443,14 @@
     <t>Appointment.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -472,6 +472,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0</t>
+  </si>
+  <si>
     <t>Appointment.meta.security</t>
   </si>
   <si>
@@ -494,7 +497,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -518,7 +521,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -561,7 +564,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -637,14 +640,15 @@
     <t>appointmentOperator</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment-operator}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment-operator|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Appointment Operator Extension</t>
   </si>
   <si>
-    <t>This extension adds the element appointmentOperator to the Appointment resource (operator of creation/update/cancel of the appointment | Cette extension ajoute l'élément appointmentOperator à la ressource Appointment (opérateur de création/modification/annulation du RDV)</t>
+    <t>Cette extension ajoute l'élément appointmentOperator à la ressource Appointment (opérateur de création/modification/annulation du RDV). 
+This extension adds the element appointmentOperator to the Appointment resource (operator of creation/update/cancel of the appointment</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -745,7 +749,7 @@
     <t>The coded reason for the appointment being cancelled. This is often used in reporting/billing/futher processing to determine if further actions are required, or specific fees apply.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason|4.0.1</t>
   </si>
   <si>
     <t>Appointment.serviceCategory</t>
@@ -757,7 +761,7 @@
     <t>A broad categorization of the service that is to be performed during this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
   </si>
   <si>
     <t>n/a, might be inferred from the ServiceDeliveryLocation</t>
@@ -778,7 +782,7 @@
     <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -793,7 +797,7 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>.performer.AssignedPerson.code</t>
@@ -811,7 +815,7 @@
     <t>The style of appointment or patient that has been booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0276|3.0.0</t>
   </si>
   <si>
     <t>.code</t>
@@ -835,7 +839,7 @@
     <t>The Reason for the appointment to take place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -850,7 +854,7 @@
     <t>Appointment.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -917,7 +921,7 @@
     <t>Appointment.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1006,7 +1010,7 @@
     <t>Appointment.slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot|2.2.0)
 </t>
   </si>
   <si>
@@ -1086,7 +1090,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1173,7 +1177,7 @@
     <t>Role of participant in encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
   </si>
   <si>
     <t>(performer | reusableDevice | subject | location).@typeCode</t>
@@ -1185,7 +1189,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
+    <t xml:space="preserve">Reference(Device|4.0.1|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1594,15 +1598,15 @@
   <dimension ref="A1:AO50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.8125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.59375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.32421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.15234375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1613,27 +1617,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="33.4296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="32.98046875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="104.51171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="150.140625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="77.2265625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="28.44921875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="90.15234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="129.51171875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="66.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2858,7 +2862,7 @@
         <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>79</v>
@@ -2929,10 +2933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2955,16 +2959,16 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2990,13 +2994,13 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>79</v>
@@ -3014,7 +3018,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3046,10 +3050,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3072,16 +3076,16 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3107,13 +3111,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3131,7 +3135,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3163,10 +3167,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3192,13 +3196,13 @@
         <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3248,7 +3252,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3280,10 +3284,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3306,16 +3310,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3341,13 +3345,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -3365,7 +3369,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3397,14 +3401,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3423,16 +3427,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3482,7 +3486,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3500,7 +3504,7 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3514,14 +3518,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3540,16 +3544,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3599,7 +3603,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3617,7 +3621,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3631,10 +3635,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3660,10 +3664,10 @@
         <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3712,7 +3716,7 @@
         <v>117</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3744,13 +3748,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>79</v>
@@ -3772,13 +3776,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3829,7 +3833,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3838,7 +3842,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>119</v>
@@ -3861,10 +3865,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3890,16 +3894,16 @@
         <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -3948,7 +3952,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3966,7 +3970,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -3980,10 +3984,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4006,13 +4010,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4063,7 +4067,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4078,27 +4082,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4121,16 +4125,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4156,13 +4160,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4180,7 +4184,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>90</v>
@@ -4195,27 +4199,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4238,13 +4242,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4271,11 +4275,11 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4293,7 +4297,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4325,10 +4329,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4351,13 +4355,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4384,11 +4388,11 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4406,7 +4410,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4424,10 +4428,10 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4438,10 +4442,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4464,16 +4468,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4499,11 +4503,11 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4521,7 +4525,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4536,10 +4540,10 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4553,10 +4557,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4579,13 +4583,13 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4612,11 +4616,11 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4634,7 +4638,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4652,13 +4656,13 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4666,10 +4670,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4692,13 +4696,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4725,11 +4729,11 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4747,7 +4751,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4765,24 +4769,24 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4805,13 +4809,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4838,13 +4842,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4862,7 +4866,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4877,10 +4881,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -4889,15 +4893,15 @@
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4920,13 +4924,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4977,7 +4981,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4992,10 +4996,10 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5009,10 +5013,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5035,16 +5039,16 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5094,7 +5098,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5109,27 +5113,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5155,10 +5159,10 @@
         <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5209,7 +5213,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5227,24 +5231,24 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5267,13 +5271,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5324,7 +5328,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5339,16 +5343,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5356,10 +5360,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5385,10 +5389,10 @@
         <v>126</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5439,7 +5443,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5454,27 +5458,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5500,10 +5504,10 @@
         <v>126</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5554,7 +5558,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5569,27 +5573,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5612,13 +5616,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5669,7 +5673,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5684,13 +5688,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5701,10 +5705,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5727,13 +5731,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5784,7 +5788,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5802,7 +5806,7 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
@@ -5816,10 +5820,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5842,16 +5846,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5901,7 +5905,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5916,13 +5920,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -5933,10 +5937,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5962,13 +5966,13 @@
         <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6018,7 +6022,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6033,27 +6037,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6079,10 +6083,10 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6133,7 +6137,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6151,28 +6155,28 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6191,13 +6195,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6248,7 +6252,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6263,10 +6267,10 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6280,10 +6284,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6306,13 +6310,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6363,7 +6367,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>90</v>
@@ -6375,30 +6379,30 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6510,10 +6514,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6627,14 +6631,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6656,16 +6660,16 @@
         <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6714,7 +6718,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6732,7 +6736,7 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -6746,10 +6750,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6772,16 +6776,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6807,13 +6811,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -6831,7 +6835,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6849,7 +6853,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>108</v>
@@ -6858,15 +6862,15 @@
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6889,13 +6893,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6946,7 +6950,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6964,24 +6968,24 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7004,13 +7008,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7037,13 +7041,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7061,7 +7065,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7079,10 +7083,10 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>79</v>
@@ -7093,10 +7097,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7119,13 +7123,13 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7152,13 +7156,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7176,7 +7180,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7194,24 +7198,24 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7234,13 +7238,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7291,7 +7295,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7323,10 +7327,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7349,16 +7353,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7408,7 +7412,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7423,10 +7427,10 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7435,7 +7439,7 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-appointment.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-appointment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="406">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Appointment|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Appointment</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -430,7 +430,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -443,14 +443,14 @@
     <t>Appointment.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -472,9 +472,6 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0</t>
-  </si>
-  <si>
     <t>Appointment.meta.security</t>
   </si>
   <si>
@@ -497,7 +494,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -521,7 +518,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -564,7 +561,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -640,15 +637,14 @@
     <t>appointmentOperator</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment-operator|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment-operator}
 </t>
   </si>
   <si>
     <t>FR Core Appointment Operator Extension</t>
   </si>
   <si>
-    <t>Cette extension ajoute l'élément appointmentOperator à la ressource Appointment (opérateur de création/modification/annulation du RDV). 
-This extension adds the element appointmentOperator to the Appointment resource (operator of creation/update/cancel of the appointment</t>
+    <t>This extension adds the element appointmentOperator to the Appointment resource (operator of creation/update/cancel of the appointment | Cette extension ajoute l'élément appointmentOperator à la ressource Appointment (opérateur de création/modification/annulation du RDV)</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -749,7 +745,7 @@
     <t>The coded reason for the appointment being cancelled. This is often used in reporting/billing/futher processing to determine if further actions are required, or specific fees apply.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason</t>
   </si>
   <si>
     <t>Appointment.serviceCategory</t>
@@ -761,7 +757,7 @@
     <t>A broad categorization of the service that is to be performed during this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category</t>
   </si>
   <si>
     <t>n/a, might be inferred from the ServiceDeliveryLocation</t>
@@ -782,7 +778,7 @@
     <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -797,7 +793,7 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
   </si>
   <si>
     <t>.performer.AssignedPerson.code</t>
@@ -815,7 +811,7 @@
     <t>The style of appointment or patient that has been booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
   </si>
   <si>
     <t>.code</t>
@@ -839,7 +835,7 @@
     <t>The Reason for the appointment to take place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -854,7 +850,7 @@
     <t>Appointment.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
+    <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -921,7 +917,7 @@
     <t>Appointment.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1010,7 +1006,7 @@
     <t>Appointment.slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot)
 </t>
   </si>
   <si>
@@ -1090,7 +1086,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -1177,7 +1173,7 @@
     <t>Role of participant in encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
   </si>
   <si>
     <t>(performer | reusableDevice | subject | location).@typeCode</t>
@@ -1189,7 +1185,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
+    <t xml:space="preserve">Reference(Device|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
 </t>
   </si>
   <si>
@@ -1598,15 +1594,15 @@
   <dimension ref="A1:AO50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.06640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.15234375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.8125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.59375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="20.32421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1617,27 +1613,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.453125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="33.4296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.44921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="90.15234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="129.51171875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="66.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="32.98046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="104.51171875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="150.140625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="77.2265625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2862,7 +2858,7 @@
         <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>147</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>79</v>
@@ -2933,10 +2929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2959,16 +2955,16 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2994,31 +2990,31 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3050,10 +3046,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3076,16 +3072,16 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3111,31 +3107,31 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3167,10 +3163,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3196,13 +3192,13 @@
         <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3252,7 +3248,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3284,10 +3280,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3310,16 +3306,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3345,31 +3341,31 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3401,14 +3397,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3427,16 +3423,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3486,7 +3482,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3504,7 +3500,7 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3518,14 +3514,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3544,16 +3540,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3603,7 +3599,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3621,7 +3617,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3635,10 +3631,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3664,10 +3660,10 @@
         <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3716,7 +3712,7 @@
         <v>117</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3748,13 +3744,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>79</v>
@@ -3776,13 +3772,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3833,7 +3829,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3842,7 +3838,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>119</v>
@@ -3865,10 +3861,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3894,16 +3890,16 @@
         <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -3952,7 +3948,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3970,7 +3966,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -3984,10 +3980,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4010,13 +4006,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4067,7 +4063,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4082,27 +4078,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4125,16 +4121,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4160,14 +4156,14 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Y22" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="Y22" t="s" s="2">
+      <c r="Z22" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Z22" t="s" s="2">
-        <v>225</v>
-      </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4184,7 +4180,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>90</v>
@@ -4199,27 +4195,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4242,13 +4238,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4275,11 +4271,11 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4297,7 +4293,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4329,10 +4325,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4355,13 +4351,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4388,11 +4384,11 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4410,7 +4406,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4428,10 +4424,10 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4442,10 +4438,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4468,16 +4464,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4503,11 +4499,11 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4525,7 +4521,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4540,10 +4536,10 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4557,10 +4553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4583,13 +4579,13 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4616,11 +4612,11 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4638,7 +4634,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4656,13 +4652,13 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4670,10 +4666,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4696,13 +4692,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4729,11 +4725,11 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4751,7 +4747,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4769,24 +4765,24 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4809,13 +4805,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4842,14 +4838,14 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
       </c>
@@ -4866,7 +4862,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4881,27 +4877,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>268</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4924,13 +4920,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4981,7 +4977,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4996,10 +4992,10 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5013,10 +5009,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5039,16 +5035,16 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5098,7 +5094,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5113,27 +5109,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5159,10 +5155,10 @@
         <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5213,7 +5209,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5231,24 +5227,24 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>289</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5271,13 +5267,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5328,7 +5324,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5343,16 +5339,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5360,10 +5356,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5389,10 +5385,10 @@
         <v>126</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5443,7 +5439,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5458,27 +5454,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5504,10 +5500,10 @@
         <v>126</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5558,7 +5554,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5573,27 +5569,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5616,13 +5612,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5673,7 +5669,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5688,13 +5684,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5705,10 +5701,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5731,13 +5727,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5788,7 +5784,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5806,7 +5802,7 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
@@ -5820,10 +5816,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5846,16 +5842,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5905,7 +5901,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5920,13 +5916,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -5937,10 +5933,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5966,13 +5962,13 @@
         <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6022,7 +6018,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6037,27 +6033,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>338</v>
-      </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6083,10 +6079,10 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6137,7 +6133,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6155,28 +6151,28 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6195,13 +6191,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6252,7 +6248,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6267,10 +6263,10 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6284,10 +6280,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6310,13 +6306,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6367,7 +6363,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>90</v>
@@ -6379,30 +6375,30 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AK41" t="s" s="2">
+      <c r="AL41" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>358</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6514,10 +6510,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6631,14 +6627,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6660,16 +6656,16 @@
         <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6718,7 +6714,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6736,7 +6732,7 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -6750,10 +6746,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6776,16 +6772,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6811,14 +6807,14 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
       </c>
@@ -6835,7 +6831,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6853,7 +6849,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>108</v>
@@ -6862,15 +6858,15 @@
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6893,13 +6889,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6950,7 +6946,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6968,24 +6964,24 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>381</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7008,13 +7004,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7041,14 +7037,14 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>386</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7065,7 +7061,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7083,10 +7079,10 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>79</v>
@@ -7097,10 +7093,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7123,13 +7119,13 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7156,14 +7152,14 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7180,7 +7176,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7198,24 +7194,24 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>396</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7238,13 +7234,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7295,7 +7291,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7327,10 +7323,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7353,16 +7349,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7412,7 +7408,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7427,19 +7423,19 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-appointment.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-appointment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="407">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Appointment</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Appointment|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -430,7 +430,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -443,14 +443,14 @@
     <t>Appointment.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -472,6 +472,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0</t>
+  </si>
+  <si>
     <t>Appointment.meta.security</t>
   </si>
   <si>
@@ -494,7 +497,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -518,7 +521,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -561,7 +564,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -637,14 +640,15 @@
     <t>appointmentOperator</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment-operator}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment-operator|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Appointment Operator Extension</t>
   </si>
   <si>
-    <t>This extension adds the element appointmentOperator to the Appointment resource (operator of creation/update/cancel of the appointment | Cette extension ajoute l'élément appointmentOperator à la ressource Appointment (opérateur de création/modification/annulation du RDV)</t>
+    <t>Cette extension ajoute l'élément appointmentOperator à la ressource Appointment (opérateur de création/modification/annulation du RDV). 
+This extension adds the element appointmentOperator to the Appointment resource (operator of creation/update/cancel of the appointment</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -745,7 +749,7 @@
     <t>The coded reason for the appointment being cancelled. This is often used in reporting/billing/futher processing to determine if further actions are required, or specific fees apply.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason|4.0.1</t>
   </si>
   <si>
     <t>Appointment.serviceCategory</t>
@@ -757,7 +761,7 @@
     <t>A broad categorization of the service that is to be performed during this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
   </si>
   <si>
     <t>n/a, might be inferred from the ServiceDeliveryLocation</t>
@@ -778,7 +782,7 @@
     <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -793,7 +797,7 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>.performer.AssignedPerson.code</t>
@@ -811,7 +815,7 @@
     <t>The style of appointment or patient that has been booked in the slot (not service type).</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0276</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0276|3.0.0</t>
   </si>
   <si>
     <t>.code</t>
@@ -835,7 +839,7 @@
     <t>The Reason for the appointment to take place.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -850,7 +854,7 @@
     <t>Appointment.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -917,7 +921,7 @@
     <t>Appointment.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1006,7 +1010,7 @@
     <t>Appointment.slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-slot|2.2.0)
 </t>
   </si>
   <si>
@@ -1086,7 +1090,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1173,7 +1177,7 @@
     <t>Role of participant in encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
   </si>
   <si>
     <t>(performer | reusableDevice | subject | location).@typeCode</t>
@@ -1185,7 +1189,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location)
+    <t xml:space="preserve">Reference(Device|4.0.1|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1594,15 +1598,15 @@
   <dimension ref="A1:AO50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.8125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.59375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.32421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.15234375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1613,27 +1617,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="33.4296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.328125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="32.98046875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="104.51171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="150.140625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="77.2265625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="28.44921875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="90.15234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="129.51171875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="66.6171875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2858,7 +2862,7 @@
         <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>79</v>
@@ -2929,10 +2933,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2955,16 +2959,16 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2990,13 +2994,13 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>79</v>
@@ -3014,7 +3018,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3046,10 +3050,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3072,16 +3076,16 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3107,13 +3111,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3131,7 +3135,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3163,10 +3167,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3192,13 +3196,13 @@
         <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3248,7 +3252,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3280,10 +3284,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3306,16 +3310,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3341,13 +3345,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -3365,7 +3369,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3397,14 +3401,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3423,16 +3427,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3482,7 +3486,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3500,7 +3504,7 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3514,14 +3518,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3540,16 +3544,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3599,7 +3603,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3617,7 +3621,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3631,10 +3635,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3660,10 +3664,10 @@
         <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3712,7 +3716,7 @@
         <v>117</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3744,13 +3748,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>79</v>
@@ -3772,13 +3776,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3829,7 +3833,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3838,7 +3842,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>119</v>
@@ -3861,10 +3865,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3890,16 +3894,16 @@
         <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -3948,7 +3952,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3966,7 +3970,7 @@
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -3980,10 +3984,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4006,13 +4010,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4063,7 +4067,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4078,27 +4082,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4121,16 +4125,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4156,13 +4160,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4180,7 +4184,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>90</v>
@@ -4195,27 +4199,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4238,13 +4242,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4271,11 +4275,11 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4293,7 +4297,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4325,10 +4329,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4351,13 +4355,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4384,11 +4388,11 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4406,7 +4410,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4424,10 +4428,10 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>79</v>
@@ -4438,10 +4442,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4464,16 +4468,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4499,11 +4503,11 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4521,7 +4525,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4536,10 +4540,10 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4553,10 +4557,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4579,13 +4583,13 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4612,11 +4616,11 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4634,7 +4638,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4652,13 +4656,13 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4666,10 +4670,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4692,13 +4696,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4725,11 +4729,11 @@
         <v>79</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>79</v>
@@ -4747,7 +4751,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4765,24 +4769,24 @@
         <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4805,13 +4809,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4838,13 +4842,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4862,7 +4866,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4877,10 +4881,10 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
@@ -4889,15 +4893,15 @@
         <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4920,13 +4924,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4977,7 +4981,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4992,10 +4996,10 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
@@ -5009,10 +5013,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5035,16 +5039,16 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5094,7 +5098,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5109,27 +5113,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5155,10 +5159,10 @@
         <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5209,7 +5213,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5227,24 +5231,24 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5267,13 +5271,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5324,7 +5328,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5339,16 +5343,16 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5356,10 +5360,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5385,10 +5389,10 @@
         <v>126</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5439,7 +5443,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5454,27 +5458,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5500,10 +5504,10 @@
         <v>126</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5554,7 +5558,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5569,27 +5573,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5612,13 +5616,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5669,7 +5673,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5684,13 +5688,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5701,10 +5705,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5727,13 +5731,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5784,7 +5788,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5802,7 +5806,7 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
@@ -5816,10 +5820,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5842,16 +5846,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5901,7 +5905,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5916,13 +5920,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -5933,10 +5937,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5962,13 +5966,13 @@
         <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6018,7 +6022,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6033,27 +6037,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6079,10 +6083,10 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6133,7 +6137,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6151,28 +6155,28 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6191,13 +6195,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6248,7 +6252,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6263,10 +6267,10 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6280,10 +6284,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6306,13 +6310,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6363,7 +6367,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>90</v>
@@ -6375,30 +6379,30 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6510,10 +6514,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6627,14 +6631,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6656,16 +6660,16 @@
         <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6714,7 +6718,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6732,7 +6736,7 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
@@ -6746,10 +6750,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6772,16 +6776,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6807,13 +6811,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -6831,7 +6835,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6849,7 +6853,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>108</v>
@@ -6858,15 +6862,15 @@
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6889,13 +6893,13 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6946,7 +6950,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6964,24 +6968,24 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7004,13 +7008,13 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7037,13 +7041,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7061,7 +7065,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7079,10 +7083,10 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>79</v>
@@ -7093,10 +7097,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7119,13 +7123,13 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7152,13 +7156,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7176,7 +7180,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7194,24 +7198,24 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7234,13 +7238,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7291,7 +7295,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7323,10 +7327,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7349,16 +7353,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7408,7 +7412,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7423,10 +7427,10 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7435,7 +7439,7 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
